--- a/data/trans_camb/P1435_2011_2023-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1435_2011_2023-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,61</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>3,67</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,23</t>
+          <t>0,64; 3,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,75</t>
+          <t>1,94; 8,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,4</t>
+          <t>2,1; 5,48</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>728,73%</t>
+          <t>720,04%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>143,26%</t>
+          <t>140,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>210,52%</t>
+          <t>206,68%</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,1; 392,86</t>
+          <t>27,29; 426,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,89; 542,39</t>
+          <t>67,05; 526,79</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,11</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>3,14</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,69</t>
+          <t>-0,0; 2,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,25</t>
+          <t>1,57; 8,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,62</t>
+          <t>1,57; 4,75</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>179,36%</t>
+          <t>192,5%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>144,88%</t>
+          <t>143,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155,22%</t>
+          <t>159,47%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 1120,37</t>
+          <t>-20,38; 1519,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,89; 450,63</t>
+          <t>20,13; 435,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,43; 407,1</t>
+          <t>50,27; 383,94</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>2,22</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,08</t>
+          <t>-0,59; 1,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 10,86</t>
+          <t>3,71; 10,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,8</t>
+          <t>1,11; 3,72</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>370,77%</t>
+          <t>364,23%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132,83%</t>
+          <t>218,66%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,39; 363,02</t>
+          <t>-72,89; 757,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,27; 1349,45</t>
+          <t>83,31; 1155,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 379,39</t>
+          <t>59,46; 674,59</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,55</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,51</t>
+          <t>2,89</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,23</t>
+          <t>0,79; 2,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 58,09</t>
+          <t>2,31; 6,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 41,83</t>
+          <t>1,83; 3,92</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1654,58%</t>
+          <t>1563,14%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560,1%</t>
+          <t>110,84%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>725,67%</t>
+          <t>167,8%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,78; 1811,71</t>
+          <t>37,72; 205,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>133,57; 2735,2</t>
+          <t>79,49; 303,01</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>1,99</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,44</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,19</t>
+          <t>0,77; 3,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,49</t>
+          <t>4,04; 8,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,28</t>
+          <t>3,03; 5,88</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>562,02%</t>
+          <t>507,1%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>148,53%</t>
+          <t>160,77%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186,49%</t>
+          <t>181,62%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32,63; —</t>
+          <t>27,96; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>55,71; 301,4</t>
+          <t>77,08; 292,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89,89; 341,44</t>
+          <t>93,15; 316,37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,41</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,73</t>
+          <t>1,97; 6,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,91</t>
+          <t>1,72; 5,04</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>115,42%</t>
+          <t>124,73%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117,53%</t>
+          <t>129,5%</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48,57; 242,85</t>
+          <t>47,49; 246,11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41,93; 236,04</t>
+          <t>51,71; 256,31</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>3,36</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,91</t>
+          <t>0,88; 1,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,73; 29,44</t>
+          <t>4,24; 6,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,94; 17,91</t>
+          <t>2,79; 3,9</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>404,26%</t>
+          <t>422,43%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>288,16%</t>
+          <t>146,53%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>300,59%</t>
+          <t>170,13%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>173,74; 986,97</t>
+          <t>166,78; 947,9</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>126,64; 808,16</t>
+          <t>102,92; 201,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>143,92; 1007,43</t>
+          <t>120,13; 229,49</t>
         </is>
       </c>
     </row>
